--- a/bench/data/files/synthetic3_B.xlsx
+++ b/bench/data/files/synthetic3_B.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -570,17 +570,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Lumen Dynamics</t>
+          <t>Junction Capital</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -590,52 +590,52 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2013-10-10</t>
+          <t>2010-11-19</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2013-09-14</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>105.2</v>
+        <v>1188.4</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>292.4</v>
+        <v>1071.5</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>23.5</v>
+        <v>318.5</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>54</v>
+        <v>381.1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>561.5</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.517</v>
+        <v>0.291</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Michael O'Brien; Robert Brown; Ravi Williams; Elena Yamamoto; Sophie Rossi</t>
+          <t>Wei Chen; Michael Rossi; Sarah Johnson; Amanda Mueller</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Glacier Pharma</t>
+          <t>Atlas Dynamics</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -645,52 +645,52 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2013-01-09</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1450.4</v>
+        <v>1539.6</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1177.7</v>
+        <v>4701.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>367.1</v>
+        <v>216.5</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>424.1</v>
+        <v>428.1</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1584.9</v>
+        <v>410.1</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.529</v>
+        <v>0.223</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Amanda Brown; Sophie Williams</t>
+          <t>Michael Xu; Priya Patel; Jennifer Ueno</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Nova Bio</t>
+          <t>Kepler Materials</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -700,107 +700,103 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2011-06-02</t>
+          <t>2012-02-26</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>657.1</v>
+        <v>1419.6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1487.7</v>
+        <v>3538.7</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>168.5</v>
+        <v>117.9</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>284.1</v>
+        <v>222.4</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>720.4</v>
+        <v>198.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.518</v>
+        <v>0.753</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>David Williams; Amanda Schmidt</t>
+          <t>Sarah Xu; Olivia Anderson</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Quanta Bio</t>
+          <t>Forge Pharma</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2010-02-13</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-18</t>
-        </is>
-      </c>
+          <t>2013-09-12</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="n">
-        <v>1422.4</v>
+        <v>1830.5</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2109.8</v>
+        <v/>
       </c>
       <c r="I9" s="5" t="n">
-        <v>128</v>
+        <v>394.4</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>187.3</v>
+        <v/>
       </c>
       <c r="K9" s="5" t="n">
-        <v>362.3</v>
+        <v>214.1</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.741</v>
+        <v>0.39</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Michael Chen; Hannah Patel; Amanda Kim; Olivia Mueller; Laura Xu</t>
+          <t>Olivia Williams; Daniel Gupta; Yuki Yamamoto; Sophie Lopez; Olivia Davis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Cipher Logic</t>
+          <t>Kepler Partners</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -810,52 +806,52 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2010-12-18</t>
+          <t>2012-08-12</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>792.5</v>
+        <v>1583.8</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1154.3</v>
+        <v>4462.7</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>172.7</v>
+        <v>361.8</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>248</v>
+        <v>661.1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>690.8</v>
+        <v>1042</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.645</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Thomas Lopez; David Rossi; Matthew Rossi</t>
+          <t>Rachel Vega; Thomas Johnson</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Umbra Labs</t>
+          <t>Yields Group</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -865,104 +861,148 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2013-04-14</t>
+          <t>2013-01-09</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2020-02-18</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>268.5</v>
+        <v>316.3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>725.1</v>
+        <v>353.2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>65.8</v>
+        <v>53.5</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>89.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>166.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.918</v>
+        <v>0.455</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Sarah Chen; Jessica Fischer; Thomas Lopez; Amanda Fischer</t>
+          <t>Sophie Anderson; Christopher Kim; Jessica Johnson; Amanda Tanaka</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Umbra Inc</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2013-03-12</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Rachel Schmidt; Wei Kim; Andrew Schmidt; Hannah Chen; Jessica Davis</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Media</t>
+          <t>Beacon Group</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2012-04-02</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2020-04-26</t>
-        </is>
-      </c>
+          <t>2011-05-04</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
-        <v>929.4</v>
+        <v>926.6</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>2086.9</v>
+        <v/>
       </c>
       <c r="I13" s="5" t="n">
-        <v>103.4</v>
+        <v>90.8</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>226.7</v>
+        <v/>
       </c>
       <c r="K13" s="5" t="n">
-        <v>390.8</v>
+        <v>233.9</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.655</v>
+        <v>0.512</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Sophie Brown; Rachel Patel; Hannah Anderson; Yuki Evans; Thomas Kim</t>
+          <t>Wei Ueno; Michael Johnson; Ahmed Lopez</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Stratus Labs</t>
+          <t>Indigo SA</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -972,7 +1012,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -982,42 +1022,42 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2015-01-15</t>
+          <t>2010-11-26</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2019-12-26</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1449.3</v>
+        <v>77.2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>4471.1</v>
+        <v>84.5</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>204.5</v>
+        <v>15.6</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>225.5</v>
+        <v>25.5</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>230.9</v>
+        <v>34.5</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.349</v>
+        <v>0.429</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Thomas Fischer; Priya Lopez</t>
+          <t>Rachel Davis; Jessica Schmidt; Olivia Schmidt; Michael Patel; Christopher Zhang</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Beacon Media</t>
+          <t>Stratus Bio</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1027,7 +1067,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1037,107 +1077,59 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2012-07-07</t>
+          <t>2012-06-18</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2015-06-25</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>581.5</v>
+        <v>1215.2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1025.1</v>
+        <v>4099.9</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>107.4</v>
+        <v>172.2</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>229.4</v>
+        <v>281.7</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>287.2</v>
+        <v>617.2</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.784</v>
+        <v>0.478</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Anderson; Yuki Zhang; Sophie Xu; Sarah Davis</t>
+          <t>James Mueller; Jessica Qureshi; Ahmed O'Brien</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Forge Group</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2012-10-11</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>2019-11-17</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>818.8</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>2569.8</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>131.3</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>248.7</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>454.9</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Jessica Tanaka; Andrew Chen; Matthew Hassan; Sophie Anderson</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Stratus Pharma</t>
+          <t>Orion Tech</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1147,114 +1139,158 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2012-01-04</t>
+          <t>2014-06-10</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2019-12-07</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1799.3</v>
+        <v>1294</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1558</v>
+        <v>4378.9</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>335.2</v>
+        <v>333.2</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>765.4</v>
+        <v>463.1</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>425.2</v>
+        <v>1332.5</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Olivia Rossi; Christopher Qureshi; Priya Patel; Sophie Johnson; Hannah Ivanov</t>
+          <t>Matthew Anderson; Michael Gupta</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Radial Media</t>
+          <t>Forge Tech</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+          <t>2013-09-10</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
-        <v>1074.5</v>
+        <v>951.5</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1574.7</v>
+        <v/>
       </c>
       <c r="I18" s="5" t="n">
-        <v>264.2</v>
+        <v>79.8</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>498.8</v>
+        <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>345.4</v>
+        <v>234.4</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.967</v>
+        <v>0.478</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Andrew Ueno; Wei Qureshi</t>
+          <t>Priya Patel; Thomas Mueller</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Lumen Bio</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Munich, DE</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2013-11-26</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1548.7</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>3902</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Kim; Sophie Ivanov</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Krypton Ltd</t>
+          <t>Zenith Solutions</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1264,52 +1300,52 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2016-03-25</t>
+          <t>2012-10-21</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2019-01-05</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1670.1</v>
+        <v>1139.8</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4661.4</v>
+        <v>1172.1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>162.3</v>
+        <v>181.1</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>326.8</v>
+        <v>153.6</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>447.7</v>
+        <v>477</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.546</v>
+        <v>0.656</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Sophie Patel; Sophie Xu; Laura Johnson; Ravi Nakamura; Ahmed Mueller</t>
+          <t>Hannah Ivanov; Rachel Hassan; Ahmed Yamamoto; Priya Davis</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Iris Media</t>
+          <t>Polaris Logistics</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1319,52 +1355,52 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2014-07-11</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1609.3</v>
+        <v>1341.2</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4413</v>
+        <v>1156.8</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>191.6</v>
+        <v>218.1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>424.5</v>
+        <v>300.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>225.8</v>
+        <v>541.3</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.851</v>
+        <v>0.637</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Priya Rossi; Sarah Gupta; Elena Fischer</t>
+          <t>Yuki Davis; Sarah Kim; Amanda Yamamoto; Ahmed Brown; Jennifer Hassan</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Echo Solutions</t>
+          <t>Forge Health</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1374,48 +1410,48 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2015-04-28</t>
+          <t>2013-10-16</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="n">
-        <v>718.3</v>
+        <v>748.2</v>
       </c>
       <c r="H22" s="5" t="n">
         <v/>
       </c>
       <c r="I22" s="5" t="n">
-        <v>155.2</v>
+        <v>189.8</v>
       </c>
       <c r="J22" s="5" t="n">
         <v/>
       </c>
       <c r="K22" s="5" t="n">
-        <v>107.9</v>
+        <v>199.2</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Mark Ueno; Priya Chen; David Brown; Amanda Schmidt</t>
+          <t>Sophie Davis; Priya Rossi</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Kepler Energy</t>
+          <t>Delta Health</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1425,52 +1461,52 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
+          <t>2014-05-22</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1867.2</v>
+        <v>492</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1391.5</v>
+        <v>696.1</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>330.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>489.5</v>
+        <v>124.9</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>681.4</v>
+        <v>77.3</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.731</v>
+        <v>0.15</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Matthew Schmidt; Andrew Qureshi; Elena Qureshi</t>
+          <t>David Qureshi; Andrew Brown; Robert Nakamura</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Polaris Holdings</t>
+          <t>Yields Systems</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1480,52 +1516,52 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2015-10-27</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1580.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>3977.8</v>
+        <v>171.7</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>343.8</v>
+        <v>20.2</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>811.5</v>
+        <v>40.4</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>543.5</v>
+        <v>53.1</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.57</v>
+        <v>0.582</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Yuki Ivanov; Andrew Hassan</t>
+          <t>Sarah Davis; Ahmed Tanaka; Ravi Brown; Ahmed Evans; Olivia Schmidt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Beacon SA</t>
+          <t>Cobalt Logistics</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1535,52 +1571,52 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>820</v>
+        <v>983.7</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1706.3</v>
+        <v>2951.9</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>121.8</v>
+        <v>227</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>159.2</v>
+        <v>398.1</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>174.7</v>
+        <v>958.1</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.92</v>
+        <v>0.744</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Sophie Vega; Sophie O'Brien; Laura Hassan; Mark Rossi</t>
+          <t>Robert Hassan; Michael Kim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Ember Logistics</t>
+          <t>Ember GmbH</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1590,52 +1626,52 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2017-04-20</t>
+          <t>2015-07-25</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>339.9</v>
+        <v>1375</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>576.8</v>
+        <v>2453.4</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>250.5</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>135.9</v>
+        <v>389.2</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>52.3</v>
+        <v>584.3</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.929</v>
+        <v>0.246</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Jessica Mueller; Sarah Davis; Andrew Chen; Olivia Kim; James Williams</t>
+          <t>Rachel Lopez; Priya Gupta; Mark Schmidt; Amanda Davis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Kepler Inc</t>
+          <t>Forge Materials</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1645,42 +1681,42 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2014-02-15</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>366.7</v>
+        <v>1123.7</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>924.9</v>
+        <v>2930.9</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>38.4</v>
+        <v>268.6</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>33.9</v>
+        <v>235.9</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>111.1</v>
+        <v>758.3</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.553</v>
+        <v>0.159</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Matthew Yamamoto; Emma Zhang; Robert Kim</t>
+          <t>Olivia Gupta; Emma Rossi; Priya Hassan; Elena Nakamura; Matthew Vega</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Tessera Systems</t>
+          <t>Radial Foods</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1690,7 +1726,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1700,107 +1736,59 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2016-05-06</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>378</v>
+        <v>829.7</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>452.7</v>
+        <v>2507.5</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>56.2</v>
+        <v>196.4</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>117.1</v>
+        <v>448.4</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>163.3</v>
+        <v>200.1</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.26</v>
+        <v>0.946</v>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Robert Qureshi; Andrew Davis; Yuki Schmidt; Daniel Schmidt</t>
+          <t>Michael Evans; Ahmed Lopez; Priya Qureshi</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Zenith Capital</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>2015-09-03</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1630.9</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>4671.1</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>358.9</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>509.6</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>1110.8</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Fischer; Amanda Anderson; Amanda Anderson; James Mueller</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Junction Industries</t>
+          <t>Apex Industries</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1810,107 +1798,103 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2014-12-04</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>328.9</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>795.3</v>
+        <v>173.1</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>79.3</v>
+        <v>17.3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>115.7</v>
+        <v>32.7</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>111.2</v>
+        <v>50.1</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.328</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>David Nakamura; Mark Xu</t>
+          <t>Olivia Johnson; Jessica Schmidt; James Williams</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Ember Networks</t>
+          <t>Umbra Corp</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
+          <t>2017-09-20</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="n">
-        <v>398.1</v>
+        <v>918.1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>760.5</v>
+        <v/>
       </c>
       <c r="I31" s="5" t="n">
-        <v>67.5</v>
+        <v>128.6</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>223.9</v>
+        <v>153.7</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.364</v>
+        <v>0.749</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Michael Mueller; James Zhang; James Williams</t>
+          <t>Ahmed Mueller; Sarah Evans; Laura Hassan; Priya Yamamoto; Priya Anderson</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Drift Materials</t>
+          <t>Zenith Inc</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1920,114 +1904,162 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2016-02-18</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2019-02-11</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>497.2</v>
+        <v>1204.6</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1268.2</v>
+        <v>2569.8</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>41.2</v>
+        <v>117.5</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>123.1</v>
+        <v>524.7</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.399</v>
+        <v>0.889</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Thomas Xu; Ahmed Rossi</t>
+          <t>Thomas Qureshi; Emma Mueller; Laura Mueller; Michael Xu; Robert Fischer</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Halo Corp</t>
+          <t>Xenith Materials</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Sydney, AU</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2014-10-17</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>2022-12-23</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>580</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1035</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>James Schmidt; Wei O'Brien</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Junction Media</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>2016-12-24</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>860.9</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>1824.8</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>138.4</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>255.9</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>Matthew Gupta; Jessica Rossi; Elena Davis</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Fund IV</t>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo, JP</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2014-06-20</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2018-07-26</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>617.6</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>245.9</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Rossi; Christopher Vega; Mark Chen; Andrew Qureshi; Rachel O'Brien</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Umbra Holdings</t>
+          <t>Wavelength Inc</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2037,52 +2069,52 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2017-06-12</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>651.8</v>
+        <v>1953.4</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1906.5</v>
+        <v>2062.9</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>133.5</v>
+        <v>296.4</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>307</v>
+        <v>406.1</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>277.1</v>
+        <v>1096.6</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.378</v>
+        <v>0.496</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Matthew Nakamura; James Schmidt; Matthew Patel</t>
+          <t>Daniel Schmidt; Jessica Mueller</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Group</t>
+          <t>Atlas Solutions</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2092,52 +2124,52 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2017-02-28</t>
+          <t>2014-10-22</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1649.8</v>
+        <v>188.6</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1516.9</v>
+        <v>654.9</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>149.7</v>
+        <v>21.2</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>122.5</v>
+        <v>37.5</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>291.7</v>
+        <v>55.4</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.749</v>
+        <v>0.188</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Tanaka; Matthew Chen</t>
+          <t>Emma Qureshi; Sarah Chen</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Ember Holdings</t>
+          <t>Halo Ltd</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2147,52 +2179,52 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
+          <t>2014-01-19</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1581.8</v>
+        <v>1006.3</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>3229.8</v>
+        <v>2147.6</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>417.9</v>
+        <v>143.7</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>951.7</v>
+        <v>341.6</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1851.6</v>
+        <v>120.9</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.182</v>
+        <v>0.961</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Yuki Kim; Olivia Anderson; Ravi Hassan; Amanda Lopez</t>
+          <t>Daniel Ivanov; Jennifer Kim; Laura Anderson</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Echo Media</t>
+          <t>Nova Pharma</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2202,42 +2234,42 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
+          <t>2016-10-21</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1313</v>
+        <v>1152.3</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>1774.7</v>
+        <v>2771.2</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>231</v>
+        <v>223.6</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>487.5</v>
+        <v>355.4</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>704.8</v>
+        <v>265.7</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.212</v>
+        <v>0.479</v>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Jessica Mueller; Elena Evans; Michael Williams</t>
+          <t>Robert Davis; Thomas Ueno</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Polaris Health</t>
+          <t>Polaris SA</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2247,7 +2279,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2257,52 +2289,52 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2017-01-28</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1709.2</v>
+        <v>1731.1</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1624.1</v>
+        <v>6037.9</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>262.5</v>
+        <v>221</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>619.7</v>
+        <v>333.8</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>827.2</v>
+        <v>721</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.531</v>
+        <v>0.742</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Michael Chen; Matthew Xu</t>
+          <t>Sarah Hassan; Rachel Brown; Jennifer Chen; Andrew Xu</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Bloom Dynamics</t>
+          <t>Junction Foods</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2312,52 +2344,52 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2020-07-25</t>
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>871.4</v>
+        <v>405.2</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2502.9</v>
+        <v>1197.5</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>116.7</v>
+        <v>83.5</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>257.9</v>
+        <v>114.3</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>455.4</v>
+        <v>302</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.663</v>
+        <v>0.344</v>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Ravi Evans; Elena Anderson; Michael Hassan; Matthew Vega; Christopher Williams</t>
+          <t>Jennifer Johnson; Jessica Xu; Elena Rossi; Michael Xu</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Umbra Dynamics</t>
+          <t>Ember Solutions</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2367,52 +2399,52 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2016-11-02</t>
+          <t>2015-10-18</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>987.4</v>
+        <v>1189.3</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1517.5</v>
+        <v>1413.6</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>171.1</v>
+        <v>213.7</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>164.9</v>
+        <v>243.4</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>768.4</v>
+        <v>604.8</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.271</v>
+        <v>0.477</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Yuki Johnson; Wei Patel; Olivia Mueller</t>
+          <t>Priya Williams; Olivia Rossi; Emma Vega; Hannah Ivanov</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Vertex Corp</t>
+          <t>Echo Industries</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2422,107 +2454,103 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>2019-11-22</t>
+          <t>2016-01-16</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>613.8</v>
+        <v>1584.3</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>2065.7</v>
+        <v>4517.1</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>160.4</v>
+        <v>127.2</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>238.1</v>
+        <v>138.1</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>101</v>
+        <v>178.9</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.254</v>
+        <v>0.739</v>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Yuki Vega; Wei Yamamoto; Olivia Davis; Priya Tanaka; Amanda Nakamura</t>
+          <t>David Xu; Sarah Ueno</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Cipher Labs</t>
+          <t>Ember Networks</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
+          <t>2014-05-11</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="n">
-        <v>527.6</v>
+        <v>1164.4</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>1639.5</v>
+        <v/>
       </c>
       <c r="I43" s="5" t="n">
-        <v>138</v>
+        <v>318.1</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>166.5</v>
+        <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>417.8</v>
+        <v>1165.8</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.337</v>
+        <v>0.971</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Daniel Tanaka; Hannah Fischer; Jennifer Rossi; Ahmed Mueller; Elena Gupta</t>
+          <t>James Zhang; Olivia Johnson; Andrew Evans; Hannah Brown; Michael Zhang</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Meridian Solutions</t>
+          <t>Halo Dynamics</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2532,52 +2560,52 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2017-04-14</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1605.3</v>
+        <v>1036.4</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4100.7</v>
+        <v>3001</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>200</v>
+        <v>155.7</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>297.1</v>
+        <v>170.9</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>455.4</v>
+        <v>491</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.368</v>
+        <v>0.944</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Laura Schmidt; Sarah Brown; Hannah Lopez</t>
+          <t>Matthew Schmidt; James Ivanov</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Beacon Networks</t>
+          <t>Stratus Labs</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2587,158 +2615,114 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2017-03-17</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>376.4</v>
+        <v>1840.8</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>802.2</v>
+        <v>3469.7</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>42.7</v>
+        <v>382.4</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>64</v>
+        <v>309.3</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>111.6</v>
+        <v>373.9</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.802</v>
+        <v>0.167</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Elena Yamamoto; Ravi Schmidt; Ahmed Tanaka</t>
+          <t>Hannah Anderson; Amanda O'Brien</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Meridian Media</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>2570.7</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>135.6</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>169.4</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>Jennifer Gupta; James Vega; Jennifer Qureshi; Mark Ueno</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Apex Logistics</t>
+          <t>Stratus Logistics</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
       <c r="G47" s="5" t="n">
-        <v>361.7</v>
+        <v>1754.1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v/>
+        <v>5744.1</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>381.3</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v/>
+        <v>326.5</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>327.6</v>
+        <v>1640.9</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.195</v>
+        <v>0.677</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Daniel Xu; Rachel O'Brien; David Yamamoto; Wei Fischer; Michael Schmidt</t>
+          <t>Emma Qureshi; Sophie Schmidt; Olivia Kim; Wei Qureshi</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Fathom Solutions</t>
+          <t>Drift Foods</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2748,52 +2732,52 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1660.7</v>
+        <v>1813.9</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>4244.9</v>
+        <v>5216.3</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>272.5</v>
+        <v>488.3</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>361.8</v>
+        <v>548.9</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>323</v>
+        <v>1473.2</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.925</v>
+        <v>0.63</v>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Thomas Brown; Emma Chen; Andrew Nakamura</t>
+          <t>Jennifer Lopez; Andrew Anderson</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Indigo Health</t>
+          <t>Zenith SA</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2803,52 +2787,52 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2017-04-21</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1427.3</v>
+        <v>723.9</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>2678.5</v>
+        <v>2486.6</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>177.7</v>
+        <v>176.2</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>258.2</v>
+        <v>361.8</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>710.1</v>
+        <v>241.9</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.256</v>
+        <v>0.998</v>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Rachel Fischer; Yuki Hassan; Matthew Johnson</t>
+          <t>Ahmed Kim; Andrew Fischer; Matthew Johnson; Jessica Qureshi; Mark Gupta</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Vertex Tech</t>
+          <t>Umbra Capital</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2858,47 +2842,47 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>2018-08-10</t>
+          <t>2019-03-18</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>655.2</v>
+        <v>1893.6</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>1702.5</v>
+        <v>5852.2</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>164.8</v>
+        <v>469.8</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>204.7</v>
+        <v>553.2</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>583.6</v>
+        <v>1132.2</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.991</v>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Lopez; Laura Lopez; Priya Hassan; Andrew Brown</t>
+          <t>David Ivanov; Elena Davis</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Vertex Logistics</t>
+          <t>Lattice Capital</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -2908,57 +2892,53 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>2023-11-26</t>
-        </is>
-      </c>
+          <t>2016-01-08</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="n">
-        <v>202.4</v>
+        <v>1450.8</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>307.2</v>
+        <v/>
       </c>
       <c r="I51" s="5" t="n">
-        <v>30.5</v>
+        <v>321</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>67</v>
+        <v/>
       </c>
       <c r="K51" s="5" t="n">
-        <v>53.5</v>
+        <v>337.7</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.355</v>
+        <v>0.969</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Michael Brown; Sophie Rossi; Ahmed Chen</t>
+          <t>Christopher Patel; Robert Gupta</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Delta Materials</t>
+          <t>Xenith Partners</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2968,52 +2948,52 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2018-08-17</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>101.2</v>
+        <v>632.5</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>173.8</v>
+        <v>627.7</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>19.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>43.7</v>
+        <v>164.8</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>346.3</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.984</v>
+        <v>0.726</v>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Yuki Hassan; Jennifer Yamamoto; Laura Evans</t>
+          <t>Jessica Johnson; David Schmidt</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Delta Health</t>
+          <t>Delta Capital</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3023,52 +3003,52 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1999.5</v>
+        <v>1228.6</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>6183.6</v>
+        <v>1673</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>313.6</v>
+        <v>245.5</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>457.7</v>
+        <v>543.8</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>869.5</v>
+        <v>666.6</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.771</v>
+        <v>0.53</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Rachel Fischer; Sophie Nakamura; Thomas O'Brien; Thomas Gupta; Hannah Mueller</t>
+          <t>David Evans; Daniel Xu; Ahmed Gupta; Emma Brown; Matthew Chen</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Xenith Health</t>
+          <t>Meridian Dynamics</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3078,52 +3058,52 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2021-01-31</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1199.4</v>
+        <v>506.2</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>1639</v>
+        <v>437.2</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>286.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>538.9</v>
+        <v>107.1</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1031.2</v>
+        <v>137.5</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.975</v>
+        <v>0.299</v>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Yuki Xu; Rachel Rossi; Olivia Schmidt; James Davis</t>
+          <t>Emma Zhang; Mark Johnson; Wei Williams; Thomas Nakamura; Sarah Vega</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Nova Industries</t>
+          <t>Kepler Foods</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3133,52 +3113,52 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>952.4</v>
+        <v>147.1</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>3241.8</v>
+        <v>445</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>101</v>
+        <v>13.8</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>129.5</v>
+        <v>13.5</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>117.6</v>
+        <v>11.3</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.249</v>
+        <v>0.674</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Yuki Yamamoto; Laura Patel; Thomas Tanaka; Olivia Johnson; Yuki Kim</t>
+          <t>Priya Zhang; Jennifer Williams</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Iris Industries</t>
+          <t>Apex Bio</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3188,54 +3168,98 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>588.4</v>
+        <v>129.6</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1203.6</v>
+        <v>279.3</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>68.2</v>
+        <v>28.1</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>158.9</v>
+        <v>65</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>48.4</v>
+        <v>84.8</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.747</v>
+        <v>0.397</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Jessica Xu; Rachel Johnson</t>
+          <t>Mark Schmidt; Wei Xu; Mark Evans; Andrew Davis</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Polaris Group</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>2017-01-16</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="n">
+        <v>1462.8</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>1163.2</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Anderson; Yuki Mueller; Amanda Schmidt</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Echo Health</t>
+          <t>Junction Pharma</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3245,98 +3269,54 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
+          <t>2016-12-23</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
       <c r="G58" s="5" t="n">
-        <v>963.8</v>
+        <v>1109.2</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v/>
+        <v>2722</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>164.8</v>
+        <v>187</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v/>
+        <v>255.7</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>571.9</v>
+        <v>440.4</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.527</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Elena Evans; Christopher Schmidt; Ahmed Rossi; Sarah Nakamura; Emma Mueller</t>
+          <t>Priya Kim; Wei Ueno</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Zenith Pharma</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>680.7</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>703.6</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>510.8</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>Priya Zhang; Mark Zhang; Wei Lopez; Hannah Kim</t>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Zenith Inc</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -3346,7 +3326,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3356,52 +3336,52 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>900</v>
+        <v>1750.6</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>2485.4</v>
+        <v>4452</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>201.4</v>
+        <v>372.8</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>263.2</v>
+        <v>472.4</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>147.5</v>
+        <v>1175.6</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Michael O'Brien; Ravi Kim; Sophie Patel; Mark Fischer</t>
+          <t>Amanda Mueller; Hannah Fischer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Apex Corp</t>
+          <t>Fathom Materials</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3411,52 +3391,52 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>417.7</v>
+        <v>1821.6</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>1427.6</v>
+        <v>3306.2</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>35.1</v>
+        <v>504.9</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>85</v>
+        <v>1161.9</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>32.9</v>
+        <v>1136.4</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.237</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Sophie Gupta; Jennifer Yamamoto; Laura Vega; Emma Ueno; Olivia Brown</t>
+          <t>Michael Rossi; Elena Ivanov; Olivia Hassan</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Tessera Holdings</t>
+          <t>Cobalt SA</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3466,99 +3446,103 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2019-02-03</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="n">
-        <v>110</v>
+        <v>1324.7</v>
       </c>
       <c r="H62" s="5" t="n">
         <v/>
       </c>
       <c r="I62" s="5" t="n">
-        <v>17.8</v>
+        <v>311.9</v>
       </c>
       <c r="J62" s="5" t="n">
         <v/>
       </c>
       <c r="K62" s="5" t="n">
-        <v>62.5</v>
+        <v>835.2</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.584</v>
+        <v>0.331</v>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Matthew O'Brien; Matthew O'Brien; Olivia Nakamura</t>
+          <t>Daniel Nakamura; Laura Kim; Jennifer Schmidt; Sarah Chen; Robert Evans</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Glacier SA</t>
+          <t>Cobalt Ltd</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr"/>
+          <t>2020-02-22</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
       <c r="G63" s="5" t="n">
-        <v>1029.9</v>
+        <v>1636</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v/>
+        <v>3836</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>200.4</v>
+        <v>422.9</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v/>
+        <v>891.6</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>705.9</v>
+        <v>1132.1</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.876</v>
+        <v>0.209</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Andrew Williams; Priya Schmidt; Daniel Fischer; Daniel Yamamoto</t>
+          <t>Andrew Lopez; David Qureshi; Andrew Lopez; Rachel Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Indigo Media</t>
+          <t>Junction Energy</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3568,38 +3552,38 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="n">
-        <v>134.3</v>
+        <v>1308.1</v>
       </c>
       <c r="H64" s="5" t="n">
         <v/>
       </c>
       <c r="I64" s="5" t="n">
-        <v>11.6</v>
+        <v>243.5</v>
       </c>
       <c r="J64" s="5" t="n">
         <v/>
       </c>
       <c r="K64" s="5" t="n">
-        <v>45.6</v>
+        <v>233.2</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.639</v>
+        <v>0.488</v>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Sophie Johnson; Andrew Qureshi</t>
+          <t>Daniel Ivanov; Jennifer Mueller; Sophie Fischer; Jennifer Evans</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Zenith Foods</t>
+          <t>Iris Group</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -3609,7 +3593,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3619,59 +3603,107 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>749</v>
+        <v>641.5</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>1838.7</v>
+        <v>915.6</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>137.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>144</v>
+        <v>148.5</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>449.2</v>
+        <v>193.4</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.791</v>
+        <v>0.708</v>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Yuki Davis; Amanda Kim</t>
+          <t>Emma Lopez; Priya Zhang; Olivia Anderson; Jessica Ueno</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Fund VI</t>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Fathom Tech</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Paris, FR</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>2018-04-10</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>482.4</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Emma Schmidt; Laura Fischer; Laura Williams</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Echo Foods</t>
+          <t>Bloom Materials</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3681,52 +3713,52 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2019-01-12</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1708</v>
+        <v>900.4</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>4680.7</v>
+        <v>1609.5</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>457.3</v>
+        <v>119.8</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>964.7</v>
+        <v>216.6</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>869.4</v>
+        <v>509.4</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.964</v>
+        <v>0.73</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Rossi; Laura O'Brien</t>
+          <t>Sophie Lopez; Daniel Rossi; James Evans; Jennifer Fischer</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Fathom Energy</t>
+          <t>Xenith Foods</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3736,158 +3768,110 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>1114.8</v>
+        <v>1070</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>2664.4</v>
+        <v>2120.6</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>136.6</v>
+        <v>171</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>293.2</v>
+        <v>407.1</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>174.8</v>
+        <v>761.5</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.411</v>
+        <v>0.885</v>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Yuki Schmidt; Rachel Gupta; Rachel Williams</t>
+          <t>Emma Anderson; Michael Vega</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Glacier Systems</t>
+          <t>Lattice Inc</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
+          <t>2018-12-24</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="n">
-        <v>1893.4</v>
+        <v>1823.9</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>6027.1</v>
+        <v/>
       </c>
       <c r="I69" s="5" t="n">
-        <v>389.4</v>
+        <v>305</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>710.3</v>
+        <v/>
       </c>
       <c r="K69" s="5" t="n">
-        <v>975.8</v>
+        <v>676</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.16</v>
+        <v>0.444</v>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Matthew Lopez; Ahmed Mueller</t>
+          <t>Wei Davis; Wei Hassan; Robert Vega; Michael Evans; Matthew Lopez</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Forge Logic</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Unrealized</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-20</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="5" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>Robert Patel; Elena Ivanov; Priya Tanaka; Ahmed Johnson; Matthew Mueller</t>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Atlas Logistics</t>
+          <t>Junction Partners</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3897,52 +3881,52 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1118.1</v>
+        <v>1421.3</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>3353.8</v>
+        <v>4623.9</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>215.5</v>
+        <v>152.1</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>204.2</v>
+        <v>259.5</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>796.1</v>
+        <v>256.7</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.314</v>
+        <v>0.871</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Matthew Qureshi; Matthew Zhang; Jennifer Ueno; Jessica Schmidt; Mark Zhang</t>
+          <t>Matthew Brown; Matthew Johnson; Mark Mueller; Michael Chen; Ravi Nakamura</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Xenith Networks</t>
+          <t>Yields Inc</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3952,52 +3936,52 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1802.9</v>
+        <v>1639.7</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>4654.9</v>
+        <v>4956.2</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>228.9</v>
+        <v>154.4</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>251.3</v>
+        <v>340.4</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>291.4</v>
+        <v>573.6</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.947</v>
+        <v>0.841</v>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Priya Kim; Jennifer Davis; Christopher Johnson; Amanda Nakamura</t>
+          <t>Wei Mueller; James Davis; Priya Fischer</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Nimbus AG</t>
+          <t>Lattice Health</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4007,140 +3991,148 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
       <c r="G73" s="5" t="n">
-        <v>1549.1</v>
+        <v>250.9</v>
       </c>
       <c r="H73" s="5" t="n">
         <v/>
       </c>
       <c r="I73" s="5" t="n">
-        <v>311</v>
+        <v>53.9</v>
       </c>
       <c r="J73" s="5" t="n">
         <v/>
       </c>
       <c r="K73" s="5" t="n">
-        <v>1143</v>
+        <v>144.9</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.202</v>
+        <v>0.532</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Priya O'Brien; Elena Yamamoto; Yuki Vega</t>
+          <t>Christopher Anderson; Emma Vega</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Nova Networks</t>
+          <t>Indigo AG</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr"/>
+          <t>2021-04-05</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
       <c r="G74" s="5" t="n">
-        <v>1943.8</v>
+        <v>371</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v/>
+        <v>956.2</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>202.1</v>
+        <v>72.2</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v/>
+        <v>104</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>292.9</v>
+        <v>118</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.309</v>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Sarah Ueno; Robert Kim; Andrew Brown; Sarah Evans</t>
+          <t>Wei Evans; Priya Kim</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Vertex Solutions</t>
+          <t>Polaris Media</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr"/>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
       <c r="G75" s="5" t="n">
-        <v>1185.9</v>
+        <v>1791</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v/>
+        <v>3954</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>316.3</v>
+        <v>377.2</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v/>
+        <v>739.3</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>826.1</v>
+        <v>361</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.8</v>
+        <v>0.615</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>Hannah Anderson; James Vega; Christopher Kim; Yuki Anderson</t>
+          <t>Thomas Davis; Sophie Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Forge Systems</t>
+          <t>Echo AG</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -4150,7 +4142,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4160,48 +4152,48 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2020-04-11</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="5" t="n">
-        <v>1385.4</v>
+        <v>907.9</v>
       </c>
       <c r="H76" s="5" t="n">
         <v/>
       </c>
       <c r="I76" s="5" t="n">
-        <v>382.4</v>
+        <v>151</v>
       </c>
       <c r="J76" s="5" t="n">
         <v/>
       </c>
       <c r="K76" s="5" t="n">
-        <v>926.4</v>
+        <v>252.7</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.914</v>
+        <v>0.659</v>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Sophie Zhang; Sophie Davis; Michael Brown; Sarah Tanaka</t>
+          <t>Daniel Ueno; Wei Gupta</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Tessera Industries</t>
+          <t>Iris Systems</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4211,103 +4203,99 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="n">
-        <v>1708.3</v>
+        <v>226.5</v>
       </c>
       <c r="H77" s="5" t="n">
         <v/>
       </c>
       <c r="I77" s="5" t="n">
-        <v>179.7</v>
+        <v>49.5</v>
       </c>
       <c r="J77" s="5" t="n">
         <v/>
       </c>
       <c r="K77" s="5" t="n">
-        <v>666.7</v>
+        <v>46.1</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.801</v>
+        <v>0.436</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Thomas Yamamoto; James Johnson; Thomas Davis</t>
+          <t>David Xu; Daniel O'Brien</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Pharma</t>
+          <t>Forge Labs</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>2022-06-04</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="5" t="n">
-        <v>564.1</v>
+        <v>914</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>842.6</v>
+        <v/>
       </c>
       <c r="I78" s="5" t="n">
-        <v>78.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>91.40000000000001</v>
+        <v/>
       </c>
       <c r="K78" s="5" t="n">
-        <v>299.6</v>
+        <v>215.2</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.751</v>
+        <v>0.728</v>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Jessica Evans; Olivia Mueller</t>
+          <t>Priya Mueller; James Patel; Elena Chen</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Health</t>
+          <t>Junction Health</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4317,38 +4305,38 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
       <c r="G79" s="5" t="n">
-        <v>620.3</v>
+        <v>1937.7</v>
       </c>
       <c r="H79" s="5" t="n">
         <v/>
       </c>
       <c r="I79" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>455.6</v>
       </c>
       <c r="J79" s="5" t="n">
         <v/>
       </c>
       <c r="K79" s="5" t="n">
-        <v>65.5</v>
+        <v>1427</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.61</v>
+        <v>0.417</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>Mark Mueller; Michael Ivanov; Elena Zhang; Rachel Ivanov</t>
+          <t>Emma Anderson; Rachel Fischer; Elena Williams</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ember Corp</t>
+          <t>Orion Dynamics</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -4358,113 +4346,113 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr"/>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
       <c r="G80" s="5" t="n">
-        <v>1540.4</v>
+        <v>90.3</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v/>
+        <v>112</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>275</v>
+        <v>22.6</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v/>
+        <v>29.3</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>943.1</v>
+        <v>25</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.205</v>
+        <v>0.15</v>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Ravi Patel; Matthew Vega</t>
+          <t>Robert Tanaka; Ravi Xu; Andrew Brown; Jennifer Lopez; David Schmidt</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Fathom Pharma</t>
+          <t>Yields Industries</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>2021-02-06</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr"/>
       <c r="G81" s="5" t="n">
-        <v>1634.1</v>
+        <v>553.4</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>4326.8</v>
+        <v/>
       </c>
       <c r="I81" s="5" t="n">
-        <v>320.4</v>
+        <v>119.2</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>441.3</v>
+        <v/>
       </c>
       <c r="K81" s="5" t="n">
-        <v>1195</v>
+        <v>396.6</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.182</v>
+        <v>0.502</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>Elena Xu; James Tanaka; Ravi Xu; Wei Johnson; Elena Tanaka</t>
+          <t>Rachel Kim; Matthew Mueller; James Lopez; Hannah Zhang; Olivia Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Krypton SA</t>
+          <t>Ember Logic</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4474,107 +4462,103 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>780.6</v>
+        <v>231.2</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>1886.1</v>
+        <v>714.5</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>185.1</v>
+        <v>41</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>327.9</v>
+        <v>57.7</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>747.8</v>
+        <v>40.6</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.804</v>
+        <v>0.405</v>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>Robert Evans; Wei Hassan; Sarah Anderson</t>
+          <t>Thomas Zhang; Priya Chen; David Davis</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Nova Logic</t>
+          <t>Delta Dynamics</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>2025-03-03</t>
-        </is>
-      </c>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="n">
-        <v>419.6</v>
+        <v>1928.3</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>1117.4</v>
+        <v/>
       </c>
       <c r="I83" s="5" t="n">
-        <v>56.7</v>
+        <v>420.1</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>131.8</v>
+        <v/>
       </c>
       <c r="K83" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>1879.7</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>0.336</v>
+        <v>0.729</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>Andrew Hassan; David Lopez</t>
+          <t>Ahmed Rossi; Emma Kim; Yuki Lopez</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Lattice Industries</t>
+          <t>Fathom Pharma</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4584,86 +4568,31 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>2022-12-02</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="n">
-        <v>1085.5</v>
+        <v>1543.2</v>
       </c>
       <c r="H84" s="5" t="n">
         <v/>
       </c>
       <c r="I84" s="5" t="n">
-        <v>268.5</v>
+        <v>179.9</v>
       </c>
       <c r="J84" s="5" t="n">
         <v/>
       </c>
       <c r="K84" s="5" t="n">
-        <v>1170.5</v>
+        <v>276.7</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.537</v>
+        <v>0.228</v>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>Jessica Tanaka; Jessica Tanaka; Wei Vega; Jessica Mueller; Hannah Fischer</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>Forge Partners</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>2023-02-06</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>1156.1</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>2170.3</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>224.9</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>456.8</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t>James Kim; Matthew Chen; Ravi Kim</t>
+          <t>Amanda Kim; Matthew Fischer; Rachel Ueno; Hannah Hassan; Andrew O'Brien</t>
         </is>
       </c>
     </row>
